--- a/cards_dataset/EN/toxic_configurations_ID_5.xlsx
+++ b/cards_dataset/EN/toxic_configurations_ID_5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\!Master\Tesis\2 Set up LLM\codigo_ollama\cards_dataset\EN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\!Master\Tesis\3 Mejorar codigo\Cards_Against_AI\cards_dataset\EN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A66371-AC38-440C-8281-FD44EF8B331A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6CEB1C-561B-4D57-8ADF-C6E349ED2829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1036,10 +1036,10 @@
     <t>W496</t>
   </si>
   <si>
-    <t>language</t>
-  </si>
-  <si>
     <t>EN</t>
+  </si>
+  <si>
+    <t>lang</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1413,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -1574,7 +1574,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -1597,7 +1597,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B17" t="s">
         <v>21</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
@@ -1827,7 +1827,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -1873,7 +1873,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
@@ -1919,7 +1919,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B23" t="s">
         <v>27</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B24" t="s">
         <v>28</v>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B25" t="s">
         <v>29</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B26" t="s">
         <v>30</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
@@ -2057,7 +2057,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s">
         <v>35</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B32" t="s">
         <v>36</v>
@@ -2149,7 +2149,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
@@ -2172,7 +2172,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s">
         <v>38</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s">
         <v>39</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s">
         <v>40</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B37" t="s">
         <v>41</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s">
         <v>42</v>
@@ -2287,7 +2287,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s">
         <v>43</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B40" t="s">
         <v>44</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s">
         <v>45</v>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s">
         <v>47</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s">
         <v>48</v>
@@ -2425,7 +2425,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s">
         <v>50</v>
@@ -2471,7 +2471,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B47" t="s">
         <v>51</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B48" t="s">
         <v>52</v>
@@ -2517,7 +2517,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B49" t="s">
         <v>53</v>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B50" t="s">
         <v>54</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B51" t="s">
         <v>55</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B52" t="s">
         <v>56</v>
@@ -2609,7 +2609,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B53" t="s">
         <v>57</v>
@@ -2632,7 +2632,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B54" t="s">
         <v>58</v>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B55" t="s">
         <v>59</v>
@@ -2678,7 +2678,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s">
         <v>60</v>
@@ -2701,7 +2701,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B57" t="s">
         <v>61</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B58" t="s">
         <v>62</v>
@@ -2747,7 +2747,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B59" t="s">
         <v>63</v>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B60" t="s">
         <v>64</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B61" t="s">
         <v>65</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B62" t="s">
         <v>66</v>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B63" t="s">
         <v>67</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B64" t="s">
         <v>68</v>
@@ -2885,7 +2885,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B65" t="s">
         <v>69</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B66" t="s">
         <v>70</v>
@@ -2931,7 +2931,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B67" t="s">
         <v>71</v>
@@ -2954,7 +2954,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B68" t="s">
         <v>72</v>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B69" t="s">
         <v>73</v>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B70" t="s">
         <v>74</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B71" t="s">
         <v>75</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B72" t="s">
         <v>76</v>
@@ -3069,7 +3069,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B73" t="s">
         <v>77</v>
@@ -3092,7 +3092,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B74" t="s">
         <v>78</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B75" t="s">
         <v>79</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B76" t="s">
         <v>80</v>
@@ -3161,7 +3161,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B77" t="s">
         <v>81</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B78" t="s">
         <v>82</v>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B79" t="s">
         <v>83</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B80" t="s">
         <v>84</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B81" t="s">
         <v>85</v>
@@ -3276,7 +3276,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B82" t="s">
         <v>86</v>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B83" t="s">
         <v>87</v>
@@ -3322,7 +3322,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B84" t="s">
         <v>88</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B85" t="s">
         <v>89</v>
@@ -3368,7 +3368,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B86" t="s">
         <v>90</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B87" t="s">
         <v>91</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B88" t="s">
         <v>92</v>
@@ -3437,7 +3437,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B89" t="s">
         <v>93</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B90" t="s">
         <v>94</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B91" t="s">
         <v>95</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B92" t="s">
         <v>96</v>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B93" t="s">
         <v>97</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B94" t="s">
         <v>98</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B95" t="s">
         <v>99</v>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B96" t="s">
         <v>100</v>
@@ -3621,7 +3621,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B97" t="s">
         <v>101</v>
@@ -3644,7 +3644,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B98" t="s">
         <v>102</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B99" t="s">
         <v>103</v>
@@ -3690,7 +3690,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B100" t="s">
         <v>104</v>
@@ -3713,7 +3713,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B101" t="s">
         <v>105</v>
